--- a/Thesis Forecasting/outputs/random_forest_forecast/Day_Ahead_24H_RANDOM_FOREST.xlsx
+++ b/Thesis Forecasting/outputs/random_forest_forecast/Day_Ahead_24H_RANDOM_FOREST.xlsx
@@ -21,13 +21,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -451,139 +463,139 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Hour</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus1_Unit1_MW</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus1_Unit2_MW</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus2_Unit1_MW</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus2_Unit2_MW</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus2_Unit3_MW</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus4_Unit1_MW</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus4_Unit2_MW</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus4_Unit3_MW</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus5_Unit1_MW</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus5_Unit2_MW</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus6_Unit1_MW</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus6_Unit2_MW</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus6_Unit3_MW</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus6_Unit4_MW</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus6_Unit5_MW</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus7_Unit1_MW</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus7_Unit2_MW</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Total_Gen_Agus1_MW</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Total_Gen_Agus2_MW</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Total_Gen_Agus4_MW</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Total_Gen_Agus5_MW</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Total_Gen_Agus6_MW</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Total_Gen_Agus7_MW</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Total_Cascade_Generation_MW</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -665,7 +677,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -747,7 +759,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -825,11 +837,11 @@
         <v>41.6885368018397</v>
       </c>
       <c r="Z4" t="n">
-        <v>571.8290479380729</v>
+        <v>571.8290479380728</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -844,13 +856,13 @@
         <v>29.66140740488274</v>
       </c>
       <c r="E5" t="n">
-        <v>40.08794296741079</v>
+        <v>40.08794296741078</v>
       </c>
       <c r="F5" t="n">
-        <v>37.26913709776528</v>
+        <v>37.26913709776527</v>
       </c>
       <c r="G5" t="n">
-        <v>51.16627103511507</v>
+        <v>51.16627103511506</v>
       </c>
       <c r="H5" t="n">
         <v>47.16638820756444</v>
@@ -874,10 +886,10 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>47.61289949852956</v>
+        <v>47.61289949852959</v>
       </c>
       <c r="P5" t="n">
-        <v>25.75461300147042</v>
+        <v>25.75461300147043</v>
       </c>
       <c r="Q5" t="n">
         <v>50</v>
@@ -907,11 +919,11 @@
         <v>41.09865364806093</v>
       </c>
       <c r="Z5" t="n">
-        <v>571.1976489716907</v>
+        <v>571.1976489716906</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -926,13 +938,13 @@
         <v>29.59075986181907</v>
       </c>
       <c r="E6" t="n">
-        <v>39.98044731340411</v>
+        <v>39.9804473134041</v>
       </c>
       <c r="F6" t="n">
-        <v>37.05454224896812</v>
+        <v>37.05454224896811</v>
       </c>
       <c r="G6" t="n">
-        <v>51.0249641240114</v>
+        <v>51.02496412401139</v>
       </c>
       <c r="H6" t="n">
         <v>47.119399491492</v>
@@ -956,10 +968,10 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>48.31246961784987</v>
+        <v>48.31246961784986</v>
       </c>
       <c r="P6" t="n">
-        <v>25.01253663215014</v>
+        <v>25.01253663215013</v>
       </c>
       <c r="Q6" t="n">
         <v>50</v>
@@ -993,7 +1005,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -1011,10 +1023,10 @@
         <v>39.73115621240716</v>
       </c>
       <c r="F7" t="n">
-        <v>36.9250517368819</v>
+        <v>36.92505173688188</v>
       </c>
       <c r="G7" t="n">
-        <v>50.90158160392645</v>
+        <v>50.90158160392643</v>
       </c>
       <c r="H7" t="n">
         <v>47.05731018004508</v>
@@ -1041,7 +1053,7 @@
         <v>48.70607997557301</v>
       </c>
       <c r="P7" t="n">
-        <v>24.29267314942698</v>
+        <v>24.29267314942699</v>
       </c>
       <c r="Q7" t="n">
         <v>50</v>
@@ -1075,7 +1087,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1090,13 +1102,13 @@
         <v>29.30230061775383</v>
       </c>
       <c r="E8" t="n">
-        <v>39.48148363271195</v>
+        <v>39.48148363271194</v>
       </c>
       <c r="F8" t="n">
-        <v>36.78674094022101</v>
+        <v>36.786740940221</v>
       </c>
       <c r="G8" t="n">
-        <v>50.77222272216102</v>
+        <v>50.772222722161</v>
       </c>
       <c r="H8" t="n">
         <v>46.99710835076678</v>
@@ -1123,7 +1135,7 @@
         <v>49.37897687737681</v>
       </c>
       <c r="P8" t="n">
-        <v>23.81494968512317</v>
+        <v>23.81494968512318</v>
       </c>
       <c r="Q8" t="n">
         <v>50</v>
@@ -1138,7 +1150,7 @@
         <v>59.45274353405233</v>
       </c>
       <c r="U8" t="n">
-        <v>127.040447295094</v>
+        <v>127.0404472950939</v>
       </c>
       <c r="V8" t="n">
         <v>139.7765583147436</v>
@@ -1157,7 +1169,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1172,13 +1184,13 @@
         <v>29.31274614151165</v>
       </c>
       <c r="E9" t="n">
-        <v>39.27756939164084</v>
+        <v>39.27756939164083</v>
       </c>
       <c r="F9" t="n">
-        <v>36.67536736815478</v>
+        <v>36.67536736815477</v>
       </c>
       <c r="G9" t="n">
-        <v>50.63248032146259</v>
+        <v>50.63248032146257</v>
       </c>
       <c r="H9" t="n">
         <v>46.94184999594067</v>
@@ -1239,7 +1251,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1257,10 +1269,10 @@
         <v>39.11954755327994</v>
       </c>
       <c r="F10" t="n">
-        <v>36.52901083360446</v>
+        <v>36.52901083360445</v>
       </c>
       <c r="G10" t="n">
-        <v>50.48182848053806</v>
+        <v>50.48182848053804</v>
       </c>
       <c r="H10" t="n">
         <v>46.91493198459882</v>
@@ -1302,7 +1314,7 @@
         <v>59.1491458255686</v>
       </c>
       <c r="U10" t="n">
-        <v>126.1303868674225</v>
+        <v>126.1303868674224</v>
       </c>
       <c r="V10" t="n">
         <v>139.5309361624325</v>
@@ -1321,7 +1333,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1336,13 +1348,13 @@
         <v>29.27173786580631</v>
       </c>
       <c r="E11" t="n">
-        <v>38.98727125012</v>
+        <v>38.98727125011999</v>
       </c>
       <c r="F11" t="n">
-        <v>36.3962249159723</v>
+        <v>36.39622491597228</v>
       </c>
       <c r="G11" t="n">
-        <v>50.33463441286934</v>
+        <v>50.33463441286933</v>
       </c>
       <c r="H11" t="n">
         <v>46.89046039528616</v>
@@ -1403,7 +1415,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1418,13 +1430,13 @@
         <v>29.21332412481817</v>
       </c>
       <c r="E12" t="n">
-        <v>38.89547577078383</v>
+        <v>38.89547577078381</v>
       </c>
       <c r="F12" t="n">
-        <v>36.30896468291447</v>
+        <v>36.30896468291446</v>
       </c>
       <c r="G12" t="n">
-        <v>50.21893388236435</v>
+        <v>50.21893388236434</v>
       </c>
       <c r="H12" t="n">
         <v>46.86138362617515</v>
@@ -1466,7 +1478,7 @@
         <v>59.21687322848535</v>
       </c>
       <c r="U12" t="n">
-        <v>125.4233743360627</v>
+        <v>125.4233743360626</v>
       </c>
       <c r="V12" t="n">
         <v>139.337364723766</v>
@@ -1485,7 +1497,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1500,13 +1512,13 @@
         <v>29.30029242658671</v>
       </c>
       <c r="E13" t="n">
-        <v>38.80293411862309</v>
+        <v>38.80293411862307</v>
       </c>
       <c r="F13" t="n">
         <v>36.22380575039794</v>
       </c>
       <c r="G13" t="n">
-        <v>50.08360220331814</v>
+        <v>50.08360220331812</v>
       </c>
       <c r="H13" t="n">
         <v>46.83353219531427</v>
@@ -1548,7 +1560,7 @@
         <v>59.36619013368323</v>
       </c>
       <c r="U13" t="n">
-        <v>125.1103420723392</v>
+        <v>125.1103420723391</v>
       </c>
       <c r="V13" t="n">
         <v>139.2399637169837</v>
@@ -1567,7 +1579,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1582,13 +1594,13 @@
         <v>29.08597905704124</v>
       </c>
       <c r="E14" t="n">
-        <v>38.76770548189077</v>
+        <v>38.76770548189076</v>
       </c>
       <c r="F14" t="n">
-        <v>36.16641629754191</v>
+        <v>36.1664162975419</v>
       </c>
       <c r="G14" t="n">
-        <v>50.02826678298953</v>
+        <v>50.02826678298952</v>
       </c>
       <c r="H14" t="n">
         <v>46.80716972930751</v>
@@ -1649,7 +1661,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1664,13 +1676,13 @@
         <v>28.85985229148303</v>
       </c>
       <c r="E15" t="n">
-        <v>38.73017606573222</v>
+        <v>38.73017606573221</v>
       </c>
       <c r="F15" t="n">
-        <v>36.12530860399812</v>
+        <v>36.12530860399811</v>
       </c>
       <c r="G15" t="n">
-        <v>49.98453566590996</v>
+        <v>49.98453566590995</v>
       </c>
       <c r="H15" t="n">
         <v>46.77026701653267</v>
@@ -1731,7 +1743,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1746,13 +1758,13 @@
         <v>29.10678992507789</v>
       </c>
       <c r="E16" t="n">
-        <v>38.68637710643203</v>
+        <v>38.68637710643201</v>
       </c>
       <c r="F16" t="n">
-        <v>36.07775253940467</v>
+        <v>36.07775253940466</v>
       </c>
       <c r="G16" t="n">
-        <v>49.93205132083499</v>
+        <v>49.93205132083497</v>
       </c>
       <c r="H16" t="n">
         <v>46.73327486137101</v>
@@ -1794,7 +1806,7 @@
         <v>58.97369094234622</v>
       </c>
       <c r="U16" t="n">
-        <v>124.6961809666717</v>
+        <v>124.6961809666716</v>
       </c>
       <c r="V16" t="n">
         <v>138.9509872116313</v>
@@ -1813,7 +1825,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1828,13 +1840,13 @@
         <v>29.03102028938055</v>
       </c>
       <c r="E17" t="n">
-        <v>38.64051243728658</v>
+        <v>38.64051243728657</v>
       </c>
       <c r="F17" t="n">
         <v>36.06146226832769</v>
       </c>
       <c r="G17" t="n">
-        <v>49.88091507599612</v>
+        <v>49.88091507599611</v>
       </c>
       <c r="H17" t="n">
         <v>46.70040864018831</v>
@@ -1891,11 +1903,11 @@
         <v>40.86896927031095</v>
       </c>
       <c r="Z17" t="n">
-        <v>564.9379860787825</v>
+        <v>564.9379860787824</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1910,7 +1922,7 @@
         <v>29.14674607587305</v>
       </c>
       <c r="E18" t="n">
-        <v>38.61411221801262</v>
+        <v>38.61411221801261</v>
       </c>
       <c r="F18" t="n">
         <v>36.02632874018435</v>
@@ -1973,11 +1985,11 @@
         <v>40.61296259405664</v>
       </c>
       <c r="Z18" t="n">
-        <v>564.8393389296141</v>
+        <v>564.839338929614</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1995,10 +2007,10 @@
         <v>38.60274455278181</v>
       </c>
       <c r="F19" t="n">
-        <v>35.99494777117303</v>
+        <v>35.99494777117302</v>
       </c>
       <c r="G19" t="n">
-        <v>49.76267949755992</v>
+        <v>49.76267949755991</v>
       </c>
       <c r="H19" t="n">
         <v>46.63190929966305</v>
@@ -2040,7 +2052,7 @@
         <v>59.47288203796191</v>
       </c>
       <c r="U19" t="n">
-        <v>124.3603718215148</v>
+        <v>124.3603718215147</v>
       </c>
       <c r="V19" t="n">
         <v>138.6630892407303</v>
@@ -2059,7 +2071,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -2074,13 +2086,13 @@
         <v>29.18744476464651</v>
       </c>
       <c r="E20" t="n">
-        <v>38.4916843120381</v>
+        <v>38.49168431203809</v>
       </c>
       <c r="F20" t="n">
-        <v>36.10113104172845</v>
+        <v>36.10113104172844</v>
       </c>
       <c r="G20" t="n">
-        <v>49.65629748770043</v>
+        <v>49.65629748770041</v>
       </c>
       <c r="H20" t="n">
         <v>46.5971220664735</v>
@@ -2122,7 +2134,7 @@
         <v>59.12592368747497</v>
       </c>
       <c r="U20" t="n">
-        <v>124.249112841467</v>
+        <v>124.2491128414669</v>
       </c>
       <c r="V20" t="n">
         <v>138.5674502413087</v>
@@ -2137,11 +2149,11 @@
         <v>41.1123950573861</v>
       </c>
       <c r="Z20" t="n">
-        <v>564.8000399353161</v>
+        <v>564.8000399353159</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -2156,22 +2168,22 @@
         <v>29.20555904519703</v>
       </c>
       <c r="E21" t="n">
-        <v>38.37203027096583</v>
+        <v>38.37203027096582</v>
       </c>
       <c r="F21" t="n">
-        <v>36.24366898378906</v>
+        <v>36.24366898378905</v>
       </c>
       <c r="G21" t="n">
-        <v>49.52215460666428</v>
+        <v>49.52215460666427</v>
       </c>
       <c r="H21" t="n">
-        <v>46.56240112770825</v>
+        <v>46.56240112770824</v>
       </c>
       <c r="I21" t="n">
-        <v>44.54367904025186</v>
+        <v>44.54367904025185</v>
       </c>
       <c r="J21" t="n">
-        <v>47.36428160730029</v>
+        <v>47.36428160730028</v>
       </c>
       <c r="K21" t="n">
         <v>22.02396724972996</v>
@@ -2204,7 +2216,7 @@
         <v>59.16479512178694</v>
       </c>
       <c r="U21" t="n">
-        <v>124.1378538614192</v>
+        <v>124.1378538614191</v>
       </c>
       <c r="V21" t="n">
         <v>138.4703617752604</v>
@@ -2223,7 +2235,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -2241,19 +2253,19 @@
         <v>38.29495676707059</v>
       </c>
       <c r="F22" t="n">
-        <v>36.3033675525365</v>
+        <v>36.30336755253649</v>
       </c>
       <c r="G22" t="n">
         <v>49.42934926560439</v>
       </c>
       <c r="H22" t="n">
-        <v>46.52716586541331</v>
+        <v>46.52716586541329</v>
       </c>
       <c r="I22" t="n">
-        <v>44.51466257154116</v>
+        <v>44.51466257154115</v>
       </c>
       <c r="J22" t="n">
-        <v>47.33601129365451</v>
+        <v>47.33601129365449</v>
       </c>
       <c r="K22" t="n">
         <v>22.05173844700472</v>
@@ -2289,7 +2301,7 @@
         <v>124.0276735852115</v>
       </c>
       <c r="V22" t="n">
-        <v>138.377839730609</v>
+        <v>138.3778397306089</v>
       </c>
       <c r="W22" t="n">
         <v>44.01634052966378</v>
@@ -2301,11 +2313,11 @@
         <v>41.34934321229422</v>
       </c>
       <c r="Z22" t="n">
-        <v>565.146595817855</v>
+        <v>565.1465958178549</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -2326,16 +2338,16 @@
         <v>36.31894983036084</v>
       </c>
       <c r="G23" t="n">
-        <v>49.36058853855778</v>
+        <v>49.36058853855777</v>
       </c>
       <c r="H23" t="n">
         <v>46.49107975313552</v>
       </c>
       <c r="I23" t="n">
-        <v>44.48558425592386</v>
+        <v>44.48558425592385</v>
       </c>
       <c r="J23" t="n">
-        <v>47.30865367689813</v>
+        <v>47.30865367689812</v>
       </c>
       <c r="K23" t="n">
         <v>21.99361158579358</v>
@@ -2387,7 +2399,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -2402,7 +2414,7 @@
         <v>29.36439204457508</v>
       </c>
       <c r="E24" t="n">
-        <v>38.1931994573233</v>
+        <v>38.19319945732331</v>
       </c>
       <c r="F24" t="n">
         <v>36.30609737618352</v>
@@ -2411,13 +2423,13 @@
         <v>49.30801619928931</v>
       </c>
       <c r="H24" t="n">
-        <v>46.4589294471454</v>
+        <v>46.45892944714539</v>
       </c>
       <c r="I24" t="n">
-        <v>44.45659853131139</v>
+        <v>44.45659853131138</v>
       </c>
       <c r="J24" t="n">
-        <v>47.27871712947606</v>
+        <v>47.27871712947604</v>
       </c>
       <c r="K24" t="n">
         <v>21.95074191780306</v>
@@ -2469,7 +2481,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -2490,16 +2502,16 @@
         <v>36.27196575215703</v>
       </c>
       <c r="G25" t="n">
-        <v>49.25730674949225</v>
+        <v>49.25730674949226</v>
       </c>
       <c r="H25" t="n">
         <v>46.40394349736496</v>
       </c>
       <c r="I25" t="n">
-        <v>44.40667623208032</v>
+        <v>44.40667623208031</v>
       </c>
       <c r="J25" t="n">
-        <v>47.2216894572089</v>
+        <v>47.22168945720889</v>
       </c>
       <c r="K25" t="n">
         <v>21.91660055387727</v>
@@ -2535,7 +2547,7 @@
         <v>123.6686383895425</v>
       </c>
       <c r="V25" t="n">
-        <v>138.0323091866542</v>
+        <v>138.0323091866541</v>
       </c>
       <c r="W25" t="n">
         <v>43.93544988599814</v>

--- a/Thesis Forecasting/outputs/random_forest_forecast/Day_Ahead_24H_RANDOM_FOREST.xlsx
+++ b/Thesis Forecasting/outputs/random_forest_forecast/Day_Ahead_24H_RANDOM_FOREST.xlsx
@@ -640,13 +640,13 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>47.41614715248679</v>
+        <v>47.29365542531561</v>
       </c>
       <c r="P2" t="n">
-        <v>28.321941349568</v>
+        <v>28.24877632623549</v>
       </c>
       <c r="Q2" t="n">
-        <v>48.08441149794521</v>
+        <v>47.96019342102194</v>
       </c>
       <c r="R2" t="n">
         <v>21.81494466535429</v>
@@ -667,13 +667,13 @@
         <v>43.13001582680973</v>
       </c>
       <c r="X2" t="n">
-        <v>158.3225</v>
+        <v>158.002625172573</v>
       </c>
       <c r="Y2" t="n">
         <v>43.37393297984622</v>
       </c>
       <c r="Z2" t="n">
-        <v>575.3397518733947</v>
+        <v>575.0198770459677</v>
       </c>
     </row>
     <row r="3">
@@ -722,10 +722,10 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>44.87902252362228</v>
+        <v>44.87093680695329</v>
       </c>
       <c r="P3" t="n">
-        <v>26.66202747637768</v>
+        <v>26.657155053483</v>
       </c>
       <c r="Q3" t="n">
         <v>50</v>
@@ -749,13 +749,13 @@
         <v>42.59741851679561</v>
       </c>
       <c r="X3" t="n">
-        <v>156.04105</v>
+        <v>156.0280918604363</v>
       </c>
       <c r="Y3" t="n">
         <v>42.15495845990617</v>
       </c>
       <c r="Z3" t="n">
-        <v>570.4285893666587</v>
+        <v>570.4156312270951</v>
       </c>
     </row>
     <row r="4">
@@ -804,10 +804,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>46.91721250332506</v>
+        <v>46.54958392792987</v>
       </c>
       <c r="P4" t="n">
-        <v>26.11041249667492</v>
+        <v>25.90561831054565</v>
       </c>
       <c r="Q4" t="n">
         <v>50</v>
@@ -831,13 +831,13 @@
         <v>42.62680687164975</v>
       </c>
       <c r="X4" t="n">
-        <v>157.527625</v>
+        <v>156.9552022384755</v>
       </c>
       <c r="Y4" t="n">
         <v>41.6885368018397</v>
       </c>
       <c r="Z4" t="n">
-        <v>571.8290479380728</v>
+        <v>571.2566251765484</v>
       </c>
     </row>
     <row r="5">
@@ -886,10 +886,10 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>47.61289949852959</v>
+        <v>47.20093886531757</v>
       </c>
       <c r="P5" t="n">
-        <v>25.75461300147043</v>
+        <v>25.52900147605483</v>
       </c>
       <c r="Q5" t="n">
         <v>50</v>
@@ -913,13 +913,13 @@
         <v>43.29704688831825</v>
       </c>
       <c r="X5" t="n">
-        <v>157.8675125</v>
+        <v>157.2299403413724</v>
       </c>
       <c r="Y5" t="n">
         <v>41.09865364806093</v>
       </c>
       <c r="Z5" t="n">
-        <v>571.1976489716906</v>
+        <v>570.560076813063</v>
       </c>
     </row>
     <row r="6">
@@ -968,10 +968,10 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>48.31246961784986</v>
+        <v>47.90298452929319</v>
       </c>
       <c r="P6" t="n">
-        <v>25.01253663215013</v>
+        <v>24.79393097127604</v>
       </c>
       <c r="Q6" t="n">
         <v>50</v>
@@ -995,13 +995,13 @@
         <v>43.83899226414883</v>
       </c>
       <c r="X6" t="n">
-        <v>157.82500625</v>
+        <v>157.1969155005692</v>
       </c>
       <c r="Y6" t="n">
         <v>40.23018138278884</v>
       </c>
       <c r="Z6" t="n">
-        <v>570.1434364607849</v>
+        <v>569.5153457113541</v>
       </c>
     </row>
     <row r="7">
@@ -1050,19 +1050,19 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>48.70607997557301</v>
+        <v>48.32472719083246</v>
       </c>
       <c r="P7" t="n">
-        <v>24.29267314942699</v>
+        <v>24.0934956963459</v>
       </c>
       <c r="Q7" t="n">
         <v>50</v>
       </c>
       <c r="R7" t="n">
-        <v>19.85929471779943</v>
+        <v>19.86059100765223</v>
       </c>
       <c r="S7" t="n">
-        <v>19.51300652625513</v>
+        <v>19.51428021259279</v>
       </c>
       <c r="T7" t="n">
         <v>60.27303760684958</v>
@@ -1077,13 +1077,13 @@
         <v>43.52469005319531</v>
       </c>
       <c r="X7" t="n">
-        <v>157.498753125</v>
+        <v>156.9182228871784</v>
       </c>
       <c r="Y7" t="n">
-        <v>39.37230124405455</v>
+        <v>39.37487122024503</v>
       </c>
       <c r="Z7" t="n">
-        <v>568.159538309407</v>
+        <v>567.5815780477758</v>
       </c>
     </row>
     <row r="8">
@@ -1132,19 +1132,19 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>49.37897687737681</v>
+        <v>48.95109085790975</v>
       </c>
       <c r="P8" t="n">
-        <v>23.81494968512318</v>
+        <v>23.5983242514585</v>
       </c>
       <c r="Q8" t="n">
         <v>50</v>
       </c>
       <c r="R8" t="n">
-        <v>20.50823934536045</v>
+        <v>20.50953583313301</v>
       </c>
       <c r="S8" t="n">
-        <v>20.14442853303628</v>
+        <v>20.14570202145419</v>
       </c>
       <c r="T8" t="n">
         <v>59.45274353405233</v>
@@ -1159,13 +1159,13 @@
         <v>43.84857740728881</v>
       </c>
       <c r="X8" t="n">
-        <v>157.6939265625</v>
+        <v>157.0494151093683</v>
       </c>
       <c r="Y8" t="n">
-        <v>40.65266787839673</v>
+        <v>40.65523785458721</v>
       </c>
       <c r="Z8" t="n">
-        <v>568.4649209920755</v>
+        <v>567.8229795151341</v>
       </c>
     </row>
     <row r="9">
@@ -1217,16 +1217,16 @@
         <v>50</v>
       </c>
       <c r="P9" t="n">
-        <v>23.85657506408953</v>
+        <v>23.51624119024137</v>
       </c>
       <c r="Q9" t="n">
-        <v>49.67493821716049</v>
+        <v>49.34650449445244</v>
       </c>
       <c r="R9" t="n">
-        <v>20.75344629631367</v>
+        <v>20.75474199941669</v>
       </c>
       <c r="S9" t="n">
-        <v>20.41019893030716</v>
+        <v>20.41147320339461</v>
       </c>
       <c r="T9" t="n">
         <v>59.47831404564473</v>
@@ -1241,13 +1241,13 @@
         <v>44.23957245527882</v>
       </c>
       <c r="X9" t="n">
-        <v>158.03151328125</v>
+        <v>157.3627456846938</v>
       </c>
       <c r="Y9" t="n">
-        <v>41.16364522662083</v>
+        <v>41.1662152028113</v>
       </c>
       <c r="Z9" t="n">
-        <v>569.1254937311235</v>
+        <v>568.4592961107577</v>
       </c>
     </row>
     <row r="10">
@@ -1296,19 +1296,19 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>48.12695120493856</v>
+        <v>47.93231638472174</v>
       </c>
       <c r="P10" t="n">
-        <v>25.18005543568642</v>
+        <v>24.77397277631962</v>
       </c>
       <c r="Q10" t="n">
         <v>50</v>
       </c>
       <c r="R10" t="n">
-        <v>20.78374734083666</v>
+        <v>20.79058197397271</v>
       </c>
       <c r="S10" t="n">
-        <v>20.31931049276</v>
+        <v>20.32599239812182</v>
       </c>
       <c r="T10" t="n">
         <v>59.1491458255686</v>
@@ -1323,13 +1323,13 @@
         <v>44.26375516129129</v>
       </c>
       <c r="X10" t="n">
-        <v>157.807006640625</v>
+        <v>157.2062891610414</v>
       </c>
       <c r="Y10" t="n">
-        <v>41.10305783359666</v>
+        <v>41.11657437209453</v>
       </c>
       <c r="Z10" t="n">
-        <v>567.9842884909364</v>
+        <v>567.3970875498507</v>
       </c>
     </row>
     <row r="11">
@@ -1378,19 +1378,19 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>48.03411818653069</v>
+        <v>47.8389727151766</v>
       </c>
       <c r="P11" t="n">
-        <v>25.1314851337818</v>
+        <v>24.72572779876435</v>
       </c>
       <c r="Q11" t="n">
         <v>50</v>
       </c>
       <c r="R11" t="n">
-        <v>20.49036589849551</v>
+        <v>20.50278208098408</v>
       </c>
       <c r="S11" t="n">
-        <v>20.03257747308037</v>
+        <v>20.04471625766109</v>
       </c>
       <c r="T11" t="n">
         <v>59.34350979545975</v>
@@ -1405,13 +1405,13 @@
         <v>44.15756596091144</v>
       </c>
       <c r="X11" t="n">
-        <v>157.6656033203125</v>
+        <v>157.0647005139409</v>
       </c>
       <c r="Y11" t="n">
-        <v>40.52294337157588</v>
+        <v>40.54749833864518</v>
       </c>
       <c r="Z11" t="n">
-        <v>566.8429738126561</v>
+        <v>566.2666259733537</v>
       </c>
     </row>
     <row r="12">
@@ -1460,19 +1460,19 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>48.07521476631519</v>
+        <v>47.87087749365148</v>
       </c>
       <c r="P12" t="n">
-        <v>25.15298689384103</v>
+        <v>24.74221788672562</v>
       </c>
       <c r="Q12" t="n">
         <v>50</v>
       </c>
       <c r="R12" t="n">
-        <v>20.44576038852941</v>
+        <v>20.45750320695243</v>
       </c>
       <c r="S12" t="n">
-        <v>19.86766234619489</v>
+        <v>19.87907313977692</v>
       </c>
       <c r="T12" t="n">
         <v>59.21687322848535</v>
@@ -1487,13 +1487,13 @@
         <v>44.1224521570871</v>
       </c>
       <c r="X12" t="n">
-        <v>157.7282016601562</v>
+        <v>157.1130953803771</v>
       </c>
       <c r="Y12" t="n">
-        <v>40.3134227347243</v>
+        <v>40.33657634672935</v>
       </c>
       <c r="Z12" t="n">
-        <v>566.1416888402816</v>
+        <v>565.5497361725074</v>
       </c>
     </row>
     <row r="13">
@@ -1542,19 +1542,19 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>48.2374712351884</v>
+        <v>48.02355688214644</v>
       </c>
       <c r="P13" t="n">
-        <v>25.23787959488973</v>
+        <v>24.82113072256105</v>
       </c>
       <c r="Q13" t="n">
         <v>50</v>
       </c>
       <c r="R13" t="n">
-        <v>20.88951744344029</v>
+        <v>20.89706166498817</v>
       </c>
       <c r="S13" t="n">
-        <v>20.21515973678024</v>
+        <v>20.22246041493583</v>
       </c>
       <c r="T13" t="n">
         <v>59.36619013368323</v>
@@ -1569,13 +1569,13 @@
         <v>44.08529262796475</v>
       </c>
       <c r="X13" t="n">
-        <v>157.9753508300781</v>
+        <v>157.3446876047075</v>
       </c>
       <c r="Y13" t="n">
-        <v>41.10467718022053</v>
+        <v>41.119522079924</v>
       </c>
       <c r="Z13" t="n">
-        <v>566.8818165612695</v>
+        <v>566.2659982356023</v>
       </c>
     </row>
     <row r="14">
@@ -1624,19 +1624,19 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>46.53126115796824</v>
+        <v>46.58531990520488</v>
       </c>
       <c r="P14" t="n">
-        <v>24.34518925707083</v>
+        <v>24.07777328857725</v>
       </c>
       <c r="Q14" t="n">
         <v>50</v>
       </c>
       <c r="R14" t="n">
-        <v>21.34304891619041</v>
+        <v>21.360025347447</v>
       </c>
       <c r="S14" t="n">
-        <v>20.63625208439357</v>
+        <v>20.6526663238155</v>
       </c>
       <c r="T14" t="n">
         <v>58.9421976541837</v>
@@ -1651,13 +1651,13 @@
         <v>44.0154453249852</v>
       </c>
       <c r="X14" t="n">
-        <v>155.3764504150391</v>
+        <v>155.1630931937821</v>
       </c>
       <c r="Y14" t="n">
-        <v>41.97930100058398</v>
+        <v>42.0126916712625</v>
       </c>
       <c r="Z14" t="n">
-        <v>564.4191267021399</v>
+        <v>564.2391601515615</v>
       </c>
     </row>
     <row r="15">
@@ -1706,19 +1706,19 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>47.34541833217028</v>
+        <v>47.0799012828821</v>
       </c>
       <c r="P15" t="n">
-        <v>24.77115687534924</v>
+        <v>24.33339927351621</v>
       </c>
       <c r="Q15" t="n">
         <v>50</v>
       </c>
       <c r="R15" t="n">
-        <v>21.17368456676961</v>
+        <v>21.19059067998293</v>
       </c>
       <c r="S15" t="n">
-        <v>20.41659958805299</v>
+        <v>20.43290120730958</v>
       </c>
       <c r="T15" t="n">
         <v>58.48216465976965</v>
@@ -1733,13 +1733,13 @@
         <v>43.97448452515925</v>
       </c>
       <c r="X15" t="n">
-        <v>156.6165752075195</v>
+        <v>155.9133005563983</v>
       </c>
       <c r="Y15" t="n">
-        <v>41.5902841548226</v>
+        <v>41.6234918872925</v>
       </c>
       <c r="Z15" t="n">
-        <v>564.5506943611898</v>
+        <v>563.8806274425385</v>
       </c>
     </row>
     <row r="16">
@@ -1788,19 +1788,19 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>47.81296170168567</v>
+        <v>47.53863050063595</v>
       </c>
       <c r="P16" t="n">
-        <v>25.01577590207406</v>
+        <v>24.57049495362314</v>
       </c>
       <c r="Q16" t="n">
         <v>50</v>
       </c>
       <c r="R16" t="n">
-        <v>20.9663678938729</v>
+        <v>20.9838858413281</v>
       </c>
       <c r="S16" t="n">
-        <v>20.29624850327781</v>
+        <v>20.31320654849659</v>
       </c>
       <c r="T16" t="n">
         <v>58.97369094234622</v>
@@ -1815,13 +1815,13 @@
         <v>43.97252295949446</v>
       </c>
       <c r="X16" t="n">
-        <v>157.3287376037597</v>
+        <v>156.6091254542591</v>
       </c>
       <c r="Y16" t="n">
-        <v>41.26261639715071</v>
+        <v>41.29709238982468</v>
       </c>
       <c r="Z16" t="n">
-        <v>565.1847360810542</v>
+        <v>564.4995999242274</v>
       </c>
     </row>
     <row r="17">
@@ -1870,19 +1870,19 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>47.03471229194007</v>
+        <v>46.78276922888862</v>
       </c>
       <c r="P17" t="n">
-        <v>26.31630650993981</v>
+        <v>25.88037739530789</v>
       </c>
       <c r="Q17" t="n">
         <v>50</v>
       </c>
       <c r="R17" t="n">
-        <v>20.71791592185287</v>
+        <v>20.73136398458464</v>
       </c>
       <c r="S17" t="n">
-        <v>20.15105334845808</v>
+        <v>20.16413345895584</v>
       </c>
       <c r="T17" t="n">
         <v>58.80803447134171</v>
@@ -1897,13 +1897,13 @@
         <v>43.97270651406613</v>
       </c>
       <c r="X17" t="n">
-        <v>157.8510188018799</v>
+        <v>157.1631466241965</v>
       </c>
       <c r="Y17" t="n">
-        <v>40.86896927031095</v>
+        <v>40.89549744354048</v>
       </c>
       <c r="Z17" t="n">
-        <v>564.9379860787824</v>
+        <v>564.2766420743285</v>
       </c>
     </row>
     <row r="18">
@@ -1952,19 +1952,19 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>43.61213266161683</v>
+        <v>43.41756261036799</v>
       </c>
       <c r="P18" t="n">
-        <v>29.8479267393231</v>
+        <v>29.44646161489149</v>
       </c>
       <c r="Q18" t="n">
         <v>50</v>
       </c>
       <c r="R18" t="n">
-        <v>20.5882423806537</v>
+        <v>20.60023122466999</v>
       </c>
       <c r="S18" t="n">
-        <v>20.02472021340295</v>
+        <v>20.03638090996313</v>
       </c>
       <c r="T18" t="n">
         <v>59.06566162214764</v>
@@ -1979,13 +1979,13 @@
         <v>43.97029627075541</v>
       </c>
       <c r="X18" t="n">
-        <v>157.9600594009399</v>
+        <v>157.3640242252595</v>
       </c>
       <c r="Y18" t="n">
-        <v>40.61296259405664</v>
+        <v>40.63661213463313</v>
       </c>
       <c r="Z18" t="n">
-        <v>564.839338929614</v>
+        <v>564.26695329451</v>
       </c>
     </row>
     <row r="19">
@@ -2034,19 +2034,19 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>42.32695983160359</v>
+        <v>42.1751873138739</v>
       </c>
       <c r="P19" t="n">
-        <v>31.00096986886637</v>
+        <v>30.65624955418724</v>
       </c>
       <c r="Q19" t="n">
         <v>50</v>
       </c>
       <c r="R19" t="n">
-        <v>20.59895868186451</v>
+        <v>20.60858546403213</v>
       </c>
       <c r="S19" t="n">
-        <v>19.98578302416482</v>
+        <v>19.99512324289114</v>
       </c>
       <c r="T19" t="n">
         <v>59.47288203796191</v>
@@ -2061,13 +2061,13 @@
         <v>43.97412765661268</v>
       </c>
       <c r="X19" t="n">
-        <v>157.82792970047</v>
+        <v>157.3314368680611</v>
       </c>
       <c r="Y19" t="n">
-        <v>40.58474170602932</v>
+        <v>40.60370870692327</v>
       </c>
       <c r="Z19" t="n">
-        <v>564.8831421633188</v>
+        <v>564.4056163318039</v>
       </c>
     </row>
     <row r="20">
@@ -2116,19 +2116,19 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>42.84830177117978</v>
+        <v>42.69482018911886</v>
       </c>
       <c r="P20" t="n">
-        <v>30.42941307905521</v>
+        <v>30.12399885741173</v>
       </c>
       <c r="Q20" t="n">
         <v>50</v>
       </c>
       <c r="R20" t="n">
-        <v>20.87683526159622</v>
+        <v>20.88415871791736</v>
       </c>
       <c r="S20" t="n">
-        <v>20.23555979578988</v>
+        <v>20.24265829690086</v>
       </c>
       <c r="T20" t="n">
         <v>59.12592368747497</v>
@@ -2143,13 +2143,13 @@
         <v>43.96744325744439</v>
       </c>
       <c r="X20" t="n">
-        <v>157.777714850235</v>
+        <v>157.3188190465306</v>
       </c>
       <c r="Y20" t="n">
-        <v>41.1123950573861</v>
+        <v>41.12681701481822</v>
       </c>
       <c r="Z20" t="n">
-        <v>564.8000399353159</v>
+        <v>564.3555660890438</v>
       </c>
     </row>
     <row r="21">
@@ -2198,19 +2198,19 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>43.31719562114957</v>
+        <v>43.14203348254161</v>
       </c>
       <c r="P21" t="n">
-        <v>29.97711180396793</v>
+        <v>29.69051370819313</v>
       </c>
       <c r="Q21" t="n">
         <v>50</v>
       </c>
       <c r="R21" t="n">
-        <v>21.16928592322156</v>
+        <v>21.16820155108741</v>
       </c>
       <c r="S21" t="n">
-        <v>20.50708409128169</v>
+        <v>20.50603363966882</v>
       </c>
       <c r="T21" t="n">
         <v>59.16479512178694</v>
@@ -2225,13 +2225,13 @@
         <v>43.97130251936676</v>
       </c>
       <c r="X21" t="n">
-        <v>157.7943074251175</v>
+        <v>157.3325471907347</v>
       </c>
       <c r="Y21" t="n">
-        <v>41.67637001450325</v>
+        <v>41.67423519075624</v>
       </c>
       <c r="Z21" t="n">
-        <v>565.214990717454</v>
+        <v>564.7510956593242</v>
       </c>
     </row>
     <row r="22">
@@ -2280,19 +2280,19 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>43.6784184084262</v>
+        <v>43.48618230937074</v>
       </c>
       <c r="P22" t="n">
-        <v>29.57253530413255</v>
+        <v>29.30297577927797</v>
       </c>
       <c r="Q22" t="n">
         <v>50</v>
       </c>
       <c r="R22" t="n">
-        <v>21.01129929293297</v>
+        <v>21.01057010968128</v>
       </c>
       <c r="S22" t="n">
-        <v>20.33804391936124</v>
+        <v>20.33733810099221</v>
       </c>
       <c r="T22" t="n">
         <v>59.62444504751775</v>
@@ -2307,13 +2307,13 @@
         <v>44.01634052966378</v>
       </c>
       <c r="X22" t="n">
-        <v>157.7509537125588</v>
+        <v>157.2891580886487</v>
       </c>
       <c r="Y22" t="n">
-        <v>41.34934321229422</v>
+        <v>41.34790821067349</v>
       </c>
       <c r="Z22" t="n">
-        <v>565.1465958178549</v>
+        <v>564.6833651923241</v>
       </c>
     </row>
     <row r="23">
@@ -2362,19 +2362,19 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>43.89111634717568</v>
+        <v>43.69770825698051</v>
       </c>
       <c r="P23" t="n">
-        <v>29.18231050910368</v>
+        <v>28.93624794885192</v>
       </c>
       <c r="Q23" t="n">
         <v>50</v>
       </c>
       <c r="R23" t="n">
-        <v>20.73297486223188</v>
+        <v>20.73341334098356</v>
       </c>
       <c r="S23" t="n">
-        <v>20.1892813390492</v>
+        <v>20.18970831930348</v>
       </c>
       <c r="T23" t="n">
         <v>58.85169522734232</v>
@@ -2389,13 +2389,13 @@
         <v>44.01131976456341</v>
       </c>
       <c r="X23" t="n">
-        <v>157.5734268562794</v>
+        <v>157.1339562058324</v>
       </c>
       <c r="Y23" t="n">
-        <v>40.92225620128109</v>
+        <v>40.92312166028704</v>
       </c>
       <c r="Z23" t="n">
-        <v>563.5615090444275</v>
+        <v>563.1229038529865</v>
       </c>
     </row>
     <row r="24">
@@ -2444,19 +2444,19 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>44.22439834206929</v>
+        <v>44.00046198659694</v>
       </c>
       <c r="P24" t="n">
-        <v>28.96436508607037</v>
+        <v>28.71837511468768</v>
       </c>
       <c r="Q24" t="n">
         <v>50</v>
       </c>
       <c r="R24" t="n">
-        <v>20.52538666662094</v>
+        <v>20.52194025200813</v>
       </c>
       <c r="S24" t="n">
-        <v>20.03521457349928</v>
+        <v>20.03185046360949</v>
       </c>
       <c r="T24" t="n">
         <v>59.53183172936171</v>
@@ -2471,13 +2471,13 @@
         <v>43.97728454846853</v>
       </c>
       <c r="X24" t="n">
-        <v>157.6887634281397</v>
+        <v>157.2188371012846</v>
       </c>
       <c r="Y24" t="n">
-        <v>40.56060124012022</v>
+        <v>40.55379071561762</v>
       </c>
       <c r="Z24" t="n">
-        <v>563.7600390868191</v>
+        <v>563.2833022354615</v>
       </c>
     </row>
     <row r="25">
@@ -2526,19 +2526,19 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>44.41877415118671</v>
+        <v>44.20174007253119</v>
       </c>
       <c r="P25" t="n">
-        <v>28.69225756288314</v>
+        <v>28.4679969648526</v>
       </c>
       <c r="Q25" t="n">
         <v>50</v>
       </c>
       <c r="R25" t="n">
-        <v>20.41674724841148</v>
+        <v>20.40971500599191</v>
       </c>
       <c r="S25" t="n">
-        <v>19.96388915899053</v>
+        <v>19.95701289674877</v>
       </c>
       <c r="T25" t="n">
         <v>59.83262576504894</v>
@@ -2553,13 +2553,13 @@
         <v>43.93544988599814</v>
       </c>
       <c r="X25" t="n">
-        <v>157.6110317140698</v>
+        <v>157.1697370373838</v>
       </c>
       <c r="Y25" t="n">
-        <v>40.38063640740201</v>
+        <v>40.36672790274068</v>
       </c>
       <c r="Z25" t="n">
-        <v>563.4606913487156</v>
+        <v>563.0054881673682</v>
       </c>
     </row>
   </sheetData>
